--- a/data/trans_orig/IQ2608_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ2608_R2-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si utilizan camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si el verano pasado utilizaron camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35144</t>
+          <t>34738</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49741</t>
+          <t>50057</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51158</t>
+          <t>51244</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66421</t>
+          <t>67032</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89979</t>
+          <t>90565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112976</t>
+          <t>111456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19214</t>
+          <t>18794</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33687</t>
+          <t>32755</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22653</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37231</t>
+          <t>37023</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45913</t>
+          <t>45554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65659</t>
+          <t>64438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17472</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17169</t>
+          <t>17185</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>16361</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31112</t>
+          <t>30591</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>16360</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>11437</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24791</t>
+          <t>24402</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59990</t>
+          <t>60260</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82857</t>
+          <t>82910</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75662</t>
+          <t>76088</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99958</t>
+          <t>99618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141364</t>
+          <t>142210</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174359</t>
+          <t>176264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,8%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84621</t>
+          <t>84642</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110360</t>
+          <t>110330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74179</t>
+          <t>71933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97085</t>
+          <t>97673</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165792</t>
+          <t>167030</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>200586</t>
+          <t>202722</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>40,02%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52766</t>
+          <t>52804</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75623</t>
+          <t>75936</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57777</t>
+          <t>57957</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79580</t>
+          <t>80571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>116052</t>
+          <t>116564</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>149178</t>
+          <t>147268</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12440</t>
+          <t>11993</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>12778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>21580</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18834</t>
+          <t>18718</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18617</t>
+          <t>19193</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34653</t>
+          <t>34957</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>19442</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33878</t>
+          <t>34413</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38688</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58194</t>
+          <t>56586</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62878</t>
+          <t>64235</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85392</t>
+          <t>86278</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27003</t>
+          <t>26857</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43399</t>
+          <t>42221</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32322</t>
+          <t>32667</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49253</t>
+          <t>50080</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63814</t>
+          <t>62805</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86686</t>
+          <t>86517</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36107</t>
+          <t>35955</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53811</t>
+          <t>53286</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26384</t>
+          <t>26278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42659</t>
+          <t>42814</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>67984</t>
+          <t>66462</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>92151</t>
+          <t>90116</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>33,49%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>11192</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>11942</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10715</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22161</t>
+          <t>23218</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7832</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19232</t>
+          <t>19063</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20770</t>
+          <t>20974</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37161</t>
+          <t>37978</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32098</t>
+          <t>32599</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50512</t>
+          <t>50699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>30373</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47868</t>
+          <t>47460</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67000</t>
+          <t>66441</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93054</t>
+          <t>92086</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54838</t>
+          <t>53971</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>76600</t>
+          <t>75905</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>52384</t>
+          <t>52281</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>73291</t>
+          <t>72692</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>112356</t>
+          <t>111939</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>141753</t>
+          <t>142823</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46336</t>
+          <t>45482</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>66700</t>
+          <t>66480</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>64271</t>
+          <t>63932</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>86072</t>
+          <t>84944</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>115405</t>
+          <t>115016</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>145619</t>
+          <t>146326</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16475</t>
+          <t>15217</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>11603</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25738</t>
+          <t>25538</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17550</t>
+          <t>17942</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32964</t>
+          <t>33273</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14902</t>
+          <t>15078</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29271</t>
+          <t>29430</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35640</t>
+          <t>36463</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>56042</t>
+          <t>57691</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>162088</t>
+          <t>162843</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>199008</t>
+          <t>197897</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>214368</t>
+          <t>211842</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>252974</t>
+          <t>252072</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>385533</t>
+          <t>388284</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>440160</t>
+          <t>440515</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>203665</t>
+          <t>205280</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>243026</t>
+          <t>243486</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>196802</t>
+          <t>196914</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>236698</t>
+          <t>236118</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>411833</t>
+          <t>411229</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>466931</t>
+          <t>466654</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>157339</t>
+          <t>157900</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>196902</t>
+          <t>192901</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>172351</t>
+          <t>170047</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>209517</t>
+          <t>207319</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>339370</t>
+          <t>337716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>393533</t>
+          <t>389525</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>15037</t>
+          <t>13983</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29625</t>
+          <t>29053</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24239</t>
+          <t>23275</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>28813</t>
+          <t>29267</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>47903</t>
+          <t>48919</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>53449</t>
+          <t>53749</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>78289</t>
+          <t>77881</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>42391</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>64869</t>
+          <t>66268</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>101775</t>
+          <t>101402</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>135665</t>
+          <t>135529</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si utilizan camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2012 (tasa de respuesta: 99,9%)</t>
+          <t>Menores según si el verano pasado utilizaron camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2012 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78448</t>
+          <t>78499</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95106</t>
+          <t>94909</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71999</t>
+          <t>72566</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89352</t>
+          <t>89238</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155703</t>
+          <t>156049</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>179968</t>
+          <t>178885</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,23%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19523</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33512</t>
+          <t>34420</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20936</t>
+          <t>20743</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36689</t>
+          <t>35595</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44529</t>
+          <t>44661</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65022</t>
+          <t>66565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>10830</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10633</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18305</t>
+          <t>18394</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8241</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15577</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111361</t>
+          <t>111927</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>137532</t>
+          <t>136516</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>135118</t>
+          <t>136599</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162943</t>
+          <t>163019</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>255425</t>
+          <t>256815</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>291986</t>
+          <t>292426</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,88%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71096</t>
+          <t>71667</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95017</t>
+          <t>95236</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71065</t>
+          <t>70380</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96411</t>
+          <t>94839</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>150199</t>
+          <t>150245</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>184551</t>
+          <t>182923</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13785</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27723</t>
+          <t>27992</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19229</t>
+          <t>18643</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35309</t>
+          <t>34659</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36988</t>
+          <t>36271</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58711</t>
+          <t>57866</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,47 +5411,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3953</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8682</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3953</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1356</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9201</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>11307</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17562</t>
+          <t>17871</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66769</t>
+          <t>66692</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87791</t>
+          <t>87620</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57675</t>
+          <t>57722</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78189</t>
+          <t>78374</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>129914</t>
+          <t>130926</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159088</t>
+          <t>159864</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34653</t>
+          <t>35236</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53912</t>
+          <t>53057</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40186</t>
+          <t>40275</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59098</t>
+          <t>59616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>80363</t>
+          <t>80557</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>106421</t>
+          <t>106930</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>17668</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33300</t>
+          <t>33046</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14699</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28360</t>
+          <t>28762</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36918</t>
+          <t>36465</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>56964</t>
+          <t>56408</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14055</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16740</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18254</t>
+          <t>18219</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13495</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29437</t>
+          <t>28519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59878</t>
+          <t>60664</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>81905</t>
+          <t>81448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65139</t>
+          <t>65205</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87408</t>
+          <t>85679</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>130938</t>
+          <t>131104</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>160885</t>
+          <t>162313</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,2%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36518</t>
+          <t>37142</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55426</t>
+          <t>55826</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49450</t>
+          <t>48024</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>69632</t>
+          <t>68915</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>90316</t>
+          <t>90626</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>118195</t>
+          <t>120030</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22600</t>
+          <t>22858</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39703</t>
+          <t>38975</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17507</t>
+          <t>17544</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32466</t>
+          <t>32630</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45566</t>
+          <t>44328</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>67573</t>
+          <t>66550</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16929</t>
+          <t>16797</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,82 +6775,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>9,8%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>7502</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>3954</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>12319</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>17628</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>11698</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>25420</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>3,33%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>3848</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>12670</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>17628</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>11447</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>25215</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20483</t>
+          <t>21168</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20034</t>
+          <t>20484</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19990</t>
+          <t>19665</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>36643</t>
+          <t>36440</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>337852</t>
+          <t>336594</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>379282</t>
+          <t>380660</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>351858</t>
+          <t>352353</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>397140</t>
+          <t>397916</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>699465</t>
+          <t>702733</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>761755</t>
+          <t>764947</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,03%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>177821</t>
+          <t>180328</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>216773</t>
+          <t>219391</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>197957</t>
+          <t>196397</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>239394</t>
+          <t>239696</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>391886</t>
+          <t>391968</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>450580</t>
+          <t>449388</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>68616</t>
+          <t>69200</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>96957</t>
+          <t>96414</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>64836</t>
+          <t>64448</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>92332</t>
+          <t>91826</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>140054</t>
+          <t>140473</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>180865</t>
+          <t>180758</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10118</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>24108</t>
+          <t>24007</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>13315</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28883</t>
+          <t>28100</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>27617</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>47234</t>
+          <t>46991</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>25715</t>
+          <t>25138</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>44514</t>
+          <t>43501</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25496</t>
+          <t>25950</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>44526</t>
+          <t>44659</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>55873</t>
+          <t>55564</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>82819</t>
+          <t>82330</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si utilizan camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2016 (tasa de respuesta: 99,76%)</t>
+          <t>Menores según si el verano pasado utilizaron camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2016 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59606</t>
+          <t>58674</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76184</t>
+          <t>76224</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55525</t>
+          <t>55175</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72617</t>
+          <t>72474</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119863</t>
+          <t>120040</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144040</t>
+          <t>144526</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,86%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20809</t>
+          <t>20277</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34945</t>
+          <t>35355</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24286</t>
+          <t>23946</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39341</t>
+          <t>39219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48834</t>
+          <t>48182</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70527</t>
+          <t>69712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18816</t>
+          <t>18627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32578</t>
+          <t>33259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12155</t>
+          <t>12029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24706</t>
+          <t>24515</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34432</t>
+          <t>33049</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53253</t>
+          <t>52363</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85344</t>
+          <t>85035</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106677</t>
+          <t>108511</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95618</t>
+          <t>96212</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121828</t>
+          <t>121669</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>187587</t>
+          <t>187698</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>221667</t>
+          <t>220869</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,14%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78700</t>
+          <t>78938</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101206</t>
+          <t>102544</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>102141</t>
+          <t>101138</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128428</t>
+          <t>127665</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>189188</t>
+          <t>188059</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>223738</t>
+          <t>221137</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,19%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11087</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>23395</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>16791</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31897</t>
+          <t>32148</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31564</t>
+          <t>31210</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52050</t>
+          <t>49875</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13867</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20367</t>
+          <t>19504</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67167</t>
+          <t>66132</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89183</t>
+          <t>89706</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69087</t>
+          <t>68743</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91623</t>
+          <t>91512</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>141699</t>
+          <t>139777</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172537</t>
+          <t>172009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60131</t>
+          <t>60678</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84034</t>
+          <t>83884</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60118</t>
+          <t>60434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83007</t>
+          <t>82581</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>128948</t>
+          <t>128288</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>160411</t>
+          <t>160927</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,63%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>19270</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34481</t>
+          <t>35771</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20653</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36860</t>
+          <t>36874</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43380</t>
+          <t>43936</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65823</t>
+          <t>66002</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>13179</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15644</t>
+          <t>15949</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,47 +9848,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>5567</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>10942</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>2,95%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>5567</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>10509</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9352</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22709</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54588</t>
+          <t>55098</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77067</t>
+          <t>75408</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53765</t>
+          <t>53759</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74592</t>
+          <t>75173</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>114931</t>
+          <t>114419</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>144172</t>
+          <t>145259</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>51242</t>
+          <t>52665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>72910</t>
+          <t>74804</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>68714</t>
+          <t>67562</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>90527</t>
+          <t>89467</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>126439</t>
+          <t>124376</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>156907</t>
+          <t>156789</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24576</t>
+          <t>25625</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42758</t>
+          <t>42228</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17170</t>
+          <t>17088</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32528</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46320</t>
+          <t>46140</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>69558</t>
+          <t>71051</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10875</t>
+          <t>11120</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>11908</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13240</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11146</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>21223</t>
+          <t>20427</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>283203</t>
+          <t>287298</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>326179</t>
+          <t>329408</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>295362</t>
+          <t>294459</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>338142</t>
+          <t>340337</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>595891</t>
+          <t>592177</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>655535</t>
+          <t>652926</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>233789</t>
+          <t>231566</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>272305</t>
+          <t>274529</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>276533</t>
+          <t>275937</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>318816</t>
+          <t>320255</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>522359</t>
+          <t>515062</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>582185</t>
+          <t>577152</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>63751</t>
+          <t>63579</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>91060</t>
+          <t>89696</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>66559</t>
+          <t>66588</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>92694</t>
+          <t>95700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>135454</t>
+          <t>136966</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>174334</t>
+          <t>176754</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7720</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20120</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>12728</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>27764</t>
+          <t>27649</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37532</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>59757</t>
+          <t>59151</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28745</t>
+          <t>29000</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>48270</t>
+          <t>47735</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>69421</t>
+          <t>70316</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>99506</t>
+          <t>98680</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si utilizan camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2023 (tasa de respuesta: 99,58%)</t>
+          <t>Menores según si el verano pasado utilizaron camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2023 (tasa de respuesta: 99,58%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10735</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11610</t>
+          <t>11543</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>19034</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8276</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14552</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,88%</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>389</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17759</t>
+          <t>17340</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20011</t>
+          <t>19966</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18846</t>
+          <t>19453</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34672</t>
+          <t>34547</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8649</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17517</t>
+          <t>17108</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13188</t>
+          <t>13041</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24421</t>
+          <t>24514</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23951</t>
+          <t>24493</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,81%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12597</t>
+          <t>12288</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17413</t>
+          <t>17237</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14794</t>
+          <t>14616</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27127</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -12685,7 +12685,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>361</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11184</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25714</t>
+          <t>26463</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16393</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33778</t>
+          <t>33016</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12922</t>
+          <t>12227</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24977</t>
+          <t>25268</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13671</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28231</t>
+          <t>27807</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29858</t>
+          <t>30496</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48376</t>
+          <t>48840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,92%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17253</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22302</t>
+          <t>22380</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20346</t>
+          <t>19107</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36536</t>
+          <t>35738</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>841</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20362</t>
+          <t>21123</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19654</t>
+          <t>19541</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20082</t>
+          <t>19514</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36753</t>
+          <t>36697</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12050</t>
+          <t>11505</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23030</t>
+          <t>23008</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26779</t>
+          <t>27428</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45271</t>
+          <t>45263</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>42379</t>
+          <t>41670</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>63691</t>
+          <t>63589</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,26%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23089</t>
+          <t>22820</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13906</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28793</t>
+          <t>28424</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28334</t>
+          <t>28717</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>46890</t>
+          <t>47678</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>891</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10285</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13440</t>
+          <t>13151</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19010</t>
+          <t>19560</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30965</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49264</t>
+          <t>49543</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>41584</t>
+          <t>41807</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>64163</t>
+          <t>64952</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>78527</t>
+          <t>78102</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>107594</t>
+          <t>107889</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>44688</t>
+          <t>43875</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>64976</t>
+          <t>64700</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>67983</t>
+          <t>67733</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>94927</t>
+          <t>93658</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>117338</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>152351</t>
+          <t>151772</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,32%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28098</t>
+          <t>29202</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45331</t>
+          <t>45475</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37694</t>
+          <t>37766</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>60235</t>
+          <t>59710</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>70643</t>
+          <t>70989</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>98230</t>
+          <t>98442</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10616</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>802</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>13434</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14979</t>
+          <t>15830</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10841</t>
+          <t>10486</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>24873</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
